--- a/iwpb-sg-dashboard/IWPB_dashboard_config_pack.xlsx
+++ b/iwpb-sg-dashboard/IWPB_dashboard_config_pack.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D72"/>
+  <dimension ref="A1:G86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -1215,6 +1215,159 @@
       <c r="B72" t="inlineStr">
         <is>
           <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>tile_hidden</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>scorecard_hidden</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>chart_note_shape</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>bubble</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>chart_note_head</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>chart_note_auto_max</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>commentary_style</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>compose</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>commentary_disclaimer</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>The Commentary has been generated from the figures in the file and the commentary document loaded with it. It may be inaccurate and/or incomplete. It is important to independently review and edit the content before further use or distribution.</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>commentary_clause_max</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>ratio_patterns</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>%|\bbps\b|\brote\b|\bcer\b|\bratio\b|headcount|\bfte\b|\bcount\b</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>commentary_driver_floor</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>commentary_driver_cover</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>commentary_max_notes</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>fsum_notes</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>fsum_note_lines</t>
         </is>
       </c>
     </row>

--- a/iwpb-sg-dashboard/IWPB_dashboard_config_pack.xlsx
+++ b/iwpb-sg-dashboard/IWPB_dashboard_config_pack.xlsx
@@ -15,9 +15,10 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Labels" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Drivers" sheetId="7" state="visible" r:id="rId7"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metrics" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ProductHierarchy" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AccountHierarchy" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CountryHierarchy" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commentary" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ProductHierarchy" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AccountHierarchy" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CountryHierarchy" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1288,7 +1289,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>The Commentary has been generated from the figures in the file and the commentary document loaded with it. It may be inaccurate and/or incomplete. It is important to independently review and edit the content before further use or distribution.</t>
+          <t>The Commentary has been generated from the figures in the file and the written commentary carried with it. It may be inaccurate and/or incomplete. It is important to independently review and edit the content before further use or distribution.</t>
         </is>
       </c>
     </row>
@@ -1377,6 +1378,1315 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G48"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="52" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="30" customWidth="1" min="6" max="6"/>
+    <col width="40" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Level 1</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Level 2</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Level 3</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Level 4</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Level 5</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Match</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>IWPB</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>B2</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>IWPB</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Retail</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Retail Banking</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>B3</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>IWPB</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Retail</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Retail Lending</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Total Consumer Assets excl Wealth Lending|Total Consumer Assets|Consumer Assets</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>B4</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>IWPB</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Retail</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Retail Lending</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Mortgages</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Mortgages (Real Estate Secured)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>B5</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>IWPB</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Retail</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Retail Lending</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Cards</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Credit Cards</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>B6</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>IWPB</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Retail</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Retail Lending</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Other Personal Lending</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>B7</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>IWPB</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Retail</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Retail Lending</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Other Personal Lending</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Payroll</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>B8</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>IWPB</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Retail</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Retail Lending</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Other Personal Lending</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Personal Loans</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>B9</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>IWPB</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Retail</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Retail Lending</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Other Personal Lending</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>B10</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>IWPB</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Retail</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Retail Lending</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Other Personal Lending</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>RBB</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>B11</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>IWPB</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Retail</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Retail Deposits</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Consumer Liabilities</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>B12</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>IWPB</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Retail</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Retail Deposits</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>CASAs</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>B13</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>IWPB</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Retail</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Retail Deposits</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>CASAs</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Current Accounts</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Current Accounts Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>B14</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>IWPB</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Retail</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Retail Deposits</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>CASAs</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Saving Accounts</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Savings and Deposit Accounts</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>B15</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>IWPB</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Retail</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Retail Deposits</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Time Deposits</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>B16</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>IWPB</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Retail</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Retail Deposits</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Retail Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>B17</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>IWPB</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Wealth</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>B18</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>IWPB</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Wealth</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Investment Distribution</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>B19</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>IWPB</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Wealth</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Investment Distribution</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Mutual Funds</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>B20</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>IWPB</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Wealth</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Investment Distribution</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Structured Products</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>B21</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>IWPB</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Wealth</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Investment Distribution</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Equities</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>B22</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>IWPB</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Wealth</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Investment Distribution</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Bonds</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>B23</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>IWPB</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Wealth</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Investment Distribution</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Wealth Lending</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>B24</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>IWPB</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Wealth</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Investment Distribution</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Other Investments</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>B25</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>IWPB</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Wealth</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Investment Distribution</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Cash FX</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>B26</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>IWPB</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Wealth</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Insurance</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>B27</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>IWPB</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Wealth</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Insurance</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Insurance Manufacturing</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>B28</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>IWPB</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Wealth</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Insurance</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Wealth Ins Distn</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Insurance Distribution|Wealth Insurance Distribution</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>B29</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>IWPB</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Wealth</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Asset Management</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>B30</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>IWPB</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Wealth</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Private Bank</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>B31</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>IWPB</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Others</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Not Used in Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>B32</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>IWPB</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Others</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Allocs of Corp Centre (RBWM)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>B33</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>IWPB</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Others</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Allocs of Corp Centre (RBWM)</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>BSM</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>B34</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>IWPB</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Others</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Allocs of Corp Centre (RBWM)</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>UK Bank Levy</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>B35</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>IWPB</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Others</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Allocs of Corp Centre (RBWM)</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Hyperinflation</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>B36</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>IWPB</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Others</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Allocs of Corp Centre (RBWM)</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Holding Int Expense</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>B37</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>IWPB</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Others</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Allocs of Corp Centre (RBWM)</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Corporate Centre Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>B38</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>IWPB</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Others</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Allocs of Corp Centre (GPB)</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>B39</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>IWPB</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Others</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Allocs of Corp Centre (GPB)</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>BSM</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>B40</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>IWPB</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Others</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Allocs of Corp Centre (GPB)</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>UK Bank Levy</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>B41</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>IWPB</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Others</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Allocs of Corp Centre (GPB)</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Hyperinflation</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>B42</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>IWPB</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Others</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Allocs of Corp Centre (GPB)</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Holding Int Expense</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>B43</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>IWPB</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Others</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Allocs of Corp Centre (GPB)</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Corporate Centre Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>B44</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>IWPB</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Others</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>B45</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>IWPB</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Others</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Non Wealth Insurance Distribution</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>B46</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>IWPB</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Others</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Other Products</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>B47</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>IWPB</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Others</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Wealth Lending</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1935,7 +3245,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4802,1301 +6112,84 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G48"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
     <col width="52" customWidth="1" min="2" max="2"/>
     <col width="30" customWidth="1" min="3" max="3"/>
-    <col width="30" customWidth="1" min="4" max="4"/>
-    <col width="30" customWidth="1" min="5" max="5"/>
-    <col width="30" customWidth="1" min="6" max="6"/>
-    <col width="40" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>ID</t>
+          <t>View</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Level 1</t>
+          <t>Line</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Level 2</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Level 3</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Level 4</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Level 5</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Match</t>
+          <t>Text</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>B1</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>IWPB</t>
+          <t>NII carried the half. Deposit margin held better than the plan assumed as the pass-through on time deposits was slower than expected.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>B2</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>IWPB</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Retail</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Retail Banking</t>
+          <t>Net Fee Income was the softer line. Investment activity thinned after the March rally and brokerage volumes have not come back, though the recurring wealth fee base is unchanged.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>B3</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>IWPB</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Retail</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Retail Lending</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Total Consumer Assets excl Wealth Lending|Total Consumer Assets|Consumer Assets</t>
+          <t>Deposits ended the half broadly flat. The migration from current accounts into time deposits continued at much the same pace as the first quarter.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>B4</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>IWPB</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Retail</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Retail Lending</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Mortgages</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Mortgages (Real Estate Secured)</t>
+          <t>Loans grew on mortgage completions that had been sitting in the pipeline since February.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>B5</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>IWPB</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Retail</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Retail Lending</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Cards</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Credit Cards</t>
+          <t>Cards spend was seasonally strong in June but the balance build is behind where the plan had it.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>B6</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>IWPB</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Retail</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Retail Lending</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Other Personal Lending</t>
+          <t>Insurance new business held up against a soft market, helped by the bancassurance push in the second quarter.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>B7</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>IWPB</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Retail</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Retail Lending</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Other Personal Lending</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Payroll</t>
+          <t>Trading Income was flat and is not expected to move materially in the second half.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>B8</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>IWPB</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Retail</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Retail Lending</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Other Personal Lending</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Personal Loans</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>B9</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>IWPB</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Retail</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Retail Lending</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Other Personal Lending</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>B10</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>IWPB</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Retail</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Retail Lending</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Other Personal Lending</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>RBB</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>B11</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>IWPB</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Retail</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Retail Deposits</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>Consumer Liabilities</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>B12</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>IWPB</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Retail</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Retail Deposits</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>CASAs</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>B13</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>IWPB</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Retail</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Retail Deposits</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>CASAs</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Current Accounts</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>Current Accounts Total</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>B14</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>IWPB</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Retail</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Retail Deposits</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>CASAs</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Saving Accounts</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>Savings and Deposit Accounts</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>B15</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>IWPB</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Retail</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Retail Deposits</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>Time Deposits</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>B16</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>IWPB</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Retail</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Retail Deposits</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>Retail Other</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>B17</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>IWPB</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Wealth</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>B18</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>IWPB</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Wealth</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Investment Distribution</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>B19</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>IWPB</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Wealth</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>Investment Distribution</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>Mutual Funds</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>B20</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>IWPB</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Wealth</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>Investment Distribution</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>Structured Products</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>B21</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>IWPB</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Wealth</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>Investment Distribution</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>Equities</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>B22</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>IWPB</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Wealth</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>Investment Distribution</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>Bonds</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>B23</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>IWPB</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Wealth</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>Investment Distribution</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>Wealth Lending</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>B24</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>IWPB</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Wealth</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>Investment Distribution</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>Other Investments</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>B25</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>IWPB</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Wealth</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>Investment Distribution</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>Cash FX</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>B26</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>IWPB</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Wealth</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>Insurance</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>B27</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>IWPB</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Wealth</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>Insurance</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>Insurance Manufacturing</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>B28</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>IWPB</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Wealth</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>Insurance</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>Wealth Ins Distn</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>Insurance Distribution|Wealth Insurance Distribution</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>B29</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>IWPB</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Wealth</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>Asset Management</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>B30</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>IWPB</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Wealth</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>Private Bank</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>B31</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>IWPB</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Others</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>Not Used in Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>B32</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>IWPB</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Others</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>Allocs of Corp Centre (RBWM)</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>B33</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>IWPB</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Others</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>Allocs of Corp Centre (RBWM)</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>BSM</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>B34</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>IWPB</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Others</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>Allocs of Corp Centre (RBWM)</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>UK Bank Levy</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>B35</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>IWPB</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Others</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>Allocs of Corp Centre (RBWM)</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>Hyperinflation</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>B36</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>IWPB</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Others</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>Allocs of Corp Centre (RBWM)</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>Holding Int Expense</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>B37</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>IWPB</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Others</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>Allocs of Corp Centre (RBWM)</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>Corporate Centre Other</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>B38</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>IWPB</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Others</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>Allocs of Corp Centre (GPB)</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>B39</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>IWPB</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Others</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>Allocs of Corp Centre (GPB)</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>BSM</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>B40</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>IWPB</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Others</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>Allocs of Corp Centre (GPB)</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>UK Bank Levy</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>B41</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>IWPB</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Others</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>Allocs of Corp Centre (GPB)</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>Hyperinflation</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>B42</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>IWPB</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Others</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>Allocs of Corp Centre (GPB)</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>Holding Int Expense</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>B43</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>IWPB</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Others</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>Allocs of Corp Centre (GPB)</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>Corporate Centre Other</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>B44</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>IWPB</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Others</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>B45</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>IWPB</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Others</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>Non Wealth Insurance Distribution</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>B46</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>IWPB</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Others</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>Other Products</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>B47</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>IWPB</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Others</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>Wealth Lending</t>
+          <t>The half closed ahead of plan on revenue, with costs the watch item into the second half.</t>
         </is>
       </c>
     </row>

--- a/iwpb-sg-dashboard/IWPB_dashboard_config_pack.xlsx
+++ b/iwpb-sg-dashboard/IWPB_dashboard_config_pack.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G86"/>
+  <dimension ref="A1:G84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -658,715 +658,691 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>rag_tolerance</t>
+          <t>fc_label_pattern</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>forecast|fcst|\bfc\b</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>rag_tolerance_options</t>
+          <t>target_label_pattern</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>0,0.03,0.05,0.10</t>
+          <t>\btarget\b|\btgt\b|target|tgt</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>fc_label_pattern</t>
+          <t>cost_patterns</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>forecast|fcst|\bfc\b</t>
+          <t>cost|\becl\b|expected\s+credit|impair|expense</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>target_label_pattern</t>
+          <t>memo_patterns</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>\btarget\b|\btgt\b|target|tgt</t>
+          <t>key metric|premier customer|\bcer\b|cost efficiency|\bfte\b|headcount|\bnnm\b|\bnnd\b|\bnnia\b|net new money|invested asset|wealth balance</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>cost_patterns</t>
+          <t>fsum_memo_label</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>cost|\becl\b|expected\s+credit|impair|expense</t>
+          <t>Key Metrics</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>memo_patterns</t>
+          <t>balance_sheet_patterns</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>key metric|premier customer|\bcer\b|cost efficiency|\bfte\b|headcount|\bnnm\b|\bnnd\b|\bnnia\b|net new money|invested asset|wealth balance</t>
+          <t>deposit|\bloan|advance|mortgage|\bcasa\b|balance|\basset|liabilit|\brwa\b|\baum\b|\bnnm\b|customer\s*account</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>fsum_memo_label</t>
+          <t>hidden_cmp_patterns</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Key Metrics</t>
+          <t>direct\s*costs?|costs?\s*[-–]?\s*(direct|indirect)|indirect\s*costs?|\becl\b|expected\s+credit</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>balance_sheet_patterns</t>
+          <t>dashboard_page_size</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>deposit|\bloan|advance|mortgage|\bcasa\b|balance|\basset|liabilit|\brwa\b|\baum\b|\bnnm\b|customer\s*account</t>
+          <t>6</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>hidden_cmp_patterns</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>direct\s*costs?|costs?\s*[-–]?\s*(direct|indirect)|indirect\s*costs?|\becl\b|expected\s+credit</t>
+          <t>font_greeting</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>dashboard_page_size</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>6</t>
+          <t>font_commentary</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>font_greeting</t>
+          <t>font_eyebrow</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>font_commentary</t>
+          <t>sim_value_width</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>50</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>font_eyebrow</t>
+          <t>month_case</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>upper</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>sim_value_width</t>
+          <t>unit_label</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>US$m</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>month_case</t>
+          <t>display_units</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>upper</t>
+          <t>as</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>unit_label</t>
+          <t>unit_options</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>US$m</t>
+          <t>as,k,mm,bn</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>display_units</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>as</t>
+          <t>unit_decimals</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>unit_options</t>
+          <t>variance_periods</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>as,k,mm,bn</t>
+          <t>auto,ytd_py,mom,mth_tgt,ytd_tgt,ytd_fc,fy_tgt,fy_py</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>unit_decimals</t>
+          <t>commentary_dim</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>variance_periods</t>
+          <t>commentary_levels</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>auto,ytd_py,mom,mth_tgt,ytd_tgt,ytd_fc,fy_tgt,fy_py</t>
+          <t>micaL1,micaL2,micaL3</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>commentary_dim</t>
+          <t>commentary_format</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>slide</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>commentary_levels</t>
+          <t>commentary_note</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>micaL1,micaL2,micaL3</t>
+          <t>ex notables</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>commentary_format</t>
+          <t>commentary_headline</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>slide</t>
+          <t>FY Forecast</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>commentary_note</t>
+          <t>commentary_fa_colours</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>ex notables</t>
+          <t>Y</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>commentary_headline</t>
+          <t>commentary_drivers</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>FY Forecast</t>
+          <t>5</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>commentary_fa_colours</t>
+          <t>fsum_title</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>Singapore: Financial Summary</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>commentary_drivers</t>
+          <t>fsum_section_label</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>P&amp;L</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>fsum_title</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>Singapore: Financial Summary</t>
+          <t>fsum_section_dim</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>fsum_section_label</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>P&amp;L</t>
+          <t>fsum_section_order</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>fsum_section_dim</t>
+          <t>fsum_sections</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>fsum_section_order</t>
+          <t>fsum_no_total</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>fsum_sections</t>
+          <t>fsum_other_label</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>fsum_no_total</t>
+          <t>fsum_total</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>auto</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>fsum_other_label</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>Other</t>
+          <t>fsum_line_order</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>fsum_total</t>
+          <t>fsum_levels</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>auto</t>
+          <t>accH1,accH2,accH3,cgL2</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>fsum_line_order</t>
+          <t>fsum_max_levels</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>6</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>fsum_levels</t>
+          <t>account_hierarchy_from</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>accH1,accH2,accH3,cgL2</t>
+          <t>mica,micaL1,micaL2,micaL3,micaL4,micaL5</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>fsum_max_levels</t>
+          <t>product_hierarchy_from</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>prodCode,prodL1,prodL2,prodL3</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>account_hierarchy_from</t>
+          <t>hierarchy_unmapped_label</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>mica,micaL1,micaL2,micaL3,micaL4,micaL5</t>
+          <t>Unmapped</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>product_hierarchy_from</t>
+          <t>fsum_ow</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>prodCode,prodL1,prodL2,prodL3</t>
+          <t>Y</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>hierarchy_unmapped_label</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>Unmapped</t>
+          <t>fsum_total_label</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>fsum_ow</t>
+          <t>fsum_residual_label</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>fsum_total_label</t>
+          <t>fsum_parent_row</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>top</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>fsum_residual_label</t>
+          <t>fsum_default_levels</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>accH1,accH2,accH3</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>fsum_parent_row</t>
+          <t>decisions_max</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>top</t>
+          <t>3</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>fsum_default_levels</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>accH1,accH2,accH3</t>
+          <t>fsum_detail</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>decisions_max</t>
+          <t>bs_unit</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>bn</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>fsum_detail</t>
+          <t>fsum_bs_label</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Balance Sheet</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>bs_unit</t>
+          <t>show_greeting</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>bn</t>
+          <t>N</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>fsum_bs_label</t>
+          <t>commentary_collapsed</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Balance Sheet</t>
+          <t>N</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>show_greeting</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>N</t>
+          <t>tile_hidden</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>commentary_collapsed</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>N</t>
+          <t>scorecard_hidden</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>tile_hidden</t>
+          <t>chart_note_shape</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>bubble</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>scorecard_hidden</t>
+          <t>chart_note_head</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>N</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>chart_note_shape</t>
+          <t>chart_note_auto_max</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>bubble</t>
+          <t>3</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>chart_note_head</t>
+          <t>commentary_style</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>compose</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>chart_note_auto_max</t>
+          <t>commentary_disclaimer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>The Commentary has been generated from the figures in the file and the written commentary carried with it. It may be inaccurate and/or incomplete. It is important to independently review and edit the content before further use or distribution.</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>commentary_style</t>
+          <t>commentary_clause_max</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>compose</t>
+          <t>150</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>commentary_disclaimer</t>
+          <t>ratio_patterns</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>The Commentary has been generated from the figures in the file and the written commentary carried with it. It may be inaccurate and/or incomplete. It is important to independently review and edit the content before further use or distribution.</t>
+          <t>%|\bbps\b|\brote\b|\bcer\b|\bratio\b|headcount|\bfte\b|\bcount\b</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>commentary_clause_max</t>
+          <t>commentary_driver_floor</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>3</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>ratio_patterns</t>
+          <t>commentary_driver_cover</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>%|\bbps\b|\brote\b|\bcer\b|\bratio\b|headcount|\bfte\b|\bcount\b</t>
+          <t>80</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>commentary_driver_floor</t>
+          <t>commentary_max_notes</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>commentary_driver_cover</t>
+          <t>fsum_notes</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>auto</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
-        <is>
-          <t>commentary_max_notes</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>fsum_notes</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
         <is>
           <t>fsum_note_lines</t>
         </is>
@@ -4629,7 +4605,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:D10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -4730,10 +4706,22 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>calc_rag_watch_at</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
           <t>calc_rag_direction</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>Y</t>
         </is>

--- a/iwpb-sg-dashboard/IWPB_dashboard_config_pack.xlsx
+++ b/iwpb-sg-dashboard/IWPB_dashboard_config_pack.xlsx
@@ -4605,7 +4605,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -4706,22 +4706,10 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>calc_rag_watch_at</t>
+          <t>calc_rag_direction</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
-        <is>
-          <t>0.05</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>calc_rag_direction</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
         <is>
           <t>Y</t>
         </is>

--- a/iwpb-sg-dashboard/IWPB_dashboard_config_pack.xlsx
+++ b/iwpb-sg-dashboard/IWPB_dashboard_config_pack.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G84"/>
+  <dimension ref="A1:G86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -536,62 +536,67 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>landing_title</t>
+          <t>group_consolidation</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Financial Performance</t>
+          <t>auto</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>total_label</t>
+          <t>group_tab_patterns</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Total P&amp;L</t>
+          <t>^group$|^consol|^group total$|^total group$</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>total_all_label</t>
+          <t>landing_title</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Total (all lines)</t>
+          <t>Financial Performance</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>total_tile</t>
+          <t>total_label</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>auto</t>
+          <t>Total P&amp;L</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>tile_lines</t>
+          <t>total_all_label</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Total (all lines)</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>tile_metrics</t>
+          <t>total_tile</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -603,50 +608,45 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>tile_dims</t>
+          <t>tile_lines</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>tile_line_levels</t>
+          <t>tile_metrics</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>micaL1,micaL2</t>
+          <t>auto</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>tile_expand_result</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Y</t>
+          <t>tile_dims</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>tile_level</t>
+          <t>tile_line_levels</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>auto</t>
+          <t>micaL1,micaL2</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>collapse_rest</t>
+          <t>tile_expand_result</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -658,691 +658,715 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>fc_label_pattern</t>
+          <t>tile_level</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>forecast|fcst|\bfc\b</t>
+          <t>auto</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>target_label_pattern</t>
+          <t>collapse_rest</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>\btarget\b|\btgt\b|target|tgt</t>
+          <t>Y</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>cost_patterns</t>
+          <t>fc_label_pattern</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>cost|\becl\b|expected\s+credit|impair|expense</t>
+          <t>forecast|fcst|\bfc\b</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>memo_patterns</t>
+          <t>target_label_pattern</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>key metric|premier customer|\bcer\b|cost efficiency|\bfte\b|headcount|\bnnm\b|\bnnd\b|\bnnia\b|net new money|invested asset|wealth balance</t>
+          <t>\btarget\b|\btgt\b|target|tgt</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>fsum_memo_label</t>
+          <t>cost_patterns</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Key Metrics</t>
+          <t>cost|\becl\b|expected\s+credit|impair|expense</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>balance_sheet_patterns</t>
+          <t>memo_patterns</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>deposit|\bloan|advance|mortgage|\bcasa\b|balance|\basset|liabilit|\brwa\b|\baum\b|\bnnm\b|customer\s*account</t>
+          <t>key metric|premier customer|\bcer\b|cost efficiency|\bfte\b|headcount|\bnnm\b|\bnnd\b|\bnnia\b|net new money|invested asset|wealth balance</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>hidden_cmp_patterns</t>
+          <t>fsum_memo_label</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>direct\s*costs?|costs?\s*[-–]?\s*(direct|indirect)|indirect\s*costs?|\becl\b|expected\s+credit</t>
+          <t>Key Metrics</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>dashboard_page_size</t>
+          <t>balance_sheet_patterns</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>deposit|\bloan|advance|mortgage|\bcasa\b|balance|\basset|liabilit|\brwa\b|\baum\b|\bnnm\b|customer\s*account</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>font_greeting</t>
+          <t>hidden_cmp_patterns</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>direct\s*costs?|costs?\s*[-–]?\s*(direct|indirect)|indirect\s*costs?|\becl\b|expected\s+credit</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>font_commentary</t>
+          <t>dashboard_page_size</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>6</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>font_eyebrow</t>
+          <t>font_greeting</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>sim_value_width</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>50</t>
+          <t>font_commentary</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>month_case</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>upper</t>
+          <t>font_eyebrow</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>unit_label</t>
+          <t>sim_value_width</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>US$m</t>
+          <t>50</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>display_units</t>
+          <t>month_case</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>as</t>
+          <t>upper</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>unit_options</t>
+          <t>unit_label</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>as,k,mm,bn</t>
+          <t>US$m</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>unit_decimals</t>
+          <t>display_units</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>as</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>variance_periods</t>
+          <t>unit_options</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>auto,ytd_py,mom,mth_tgt,ytd_tgt,ytd_fc,fy_tgt,fy_py</t>
+          <t>as,k,mm,bn</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>commentary_dim</t>
+          <t>unit_decimals</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>commentary_levels</t>
+          <t>variance_periods</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>micaL1,micaL2,micaL3</t>
+          <t>auto,ytd_py,mom,mth_tgt,ytd_tgt,ytd_fc,fy_tgt,fy_py</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>commentary_format</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>slide</t>
+          <t>commentary_dim</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>commentary_note</t>
+          <t>commentary_levels</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>ex notables</t>
+          <t>micaL1,micaL2,micaL3</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>commentary_headline</t>
+          <t>commentary_format</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>FY Forecast</t>
+          <t>slide</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>commentary_fa_colours</t>
+          <t>commentary_note</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>ex notables</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>commentary_drivers</t>
+          <t>commentary_headline</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>FY Forecast</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>fsum_title</t>
+          <t>commentary_fa_colours</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Singapore: Financial Summary</t>
+          <t>Y</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>fsum_section_label</t>
+          <t>commentary_drivers</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>P&amp;L</t>
+          <t>5</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>fsum_section_dim</t>
+          <t>fsum_title</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Singapore: Financial Summary</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>fsum_section_order</t>
+          <t>fsum_section_label</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>P&amp;L</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>fsum_sections</t>
+          <t>fsum_section_dim</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>fsum_no_total</t>
+          <t>fsum_section_order</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>fsum_other_label</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>Other</t>
+          <t>fsum_sections</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>fsum_total</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>auto</t>
+          <t>fsum_no_total</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>fsum_line_order</t>
+          <t>fsum_other_label</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>fsum_levels</t>
+          <t>fsum_total</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>accH1,accH2,accH3,cgL2</t>
+          <t>auto</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>fsum_max_levels</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>6</t>
+          <t>fsum_line_order</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>account_hierarchy_from</t>
+          <t>fsum_levels</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>mica,micaL1,micaL2,micaL3,micaL4,micaL5</t>
+          <t>accH1,accH2,accH3,cgL2</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>product_hierarchy_from</t>
+          <t>fsum_max_levels</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>prodCode,prodL1,prodL2,prodL3</t>
+          <t>6</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>hierarchy_unmapped_label</t>
+          <t>account_hierarchy_from</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Unmapped</t>
+          <t>mica,micaL1,micaL2,micaL3,micaL4,micaL5</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>fsum_ow</t>
+          <t>product_hierarchy_from</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>prodCode,prodL1,prodL2,prodL3</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>fsum_total_label</t>
+          <t>hierarchy_unmapped_label</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Unmapped</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>fsum_residual_label</t>
+          <t>fsum_ow</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Y</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>fsum_parent_row</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>top</t>
+          <t>fsum_total_label</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>fsum_default_levels</t>
+          <t>fsum_residual_label</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>accH1,accH2,accH3</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>decisions_max</t>
+          <t>fsum_parent_row</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>top</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>fsum_detail</t>
+          <t>fsum_default_levels</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>accH1,accH2,accH3</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>bs_unit</t>
+          <t>decisions_max</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>bn</t>
+          <t>3</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>fsum_bs_label</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>Balance Sheet</t>
+          <t>fsum_detail</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>show_greeting</t>
+          <t>bs_unit</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>bn</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>commentary_collapsed</t>
+          <t>fsum_bs_label</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Balance Sheet</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>tile_hidden</t>
+          <t>show_greeting</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>N</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>scorecard_hidden</t>
+          <t>commentary_collapsed</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>N</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>chart_note_shape</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>bubble</t>
+          <t>tile_hidden</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>chart_note_head</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>N</t>
+          <t>scorecard_hidden</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>chart_note_auto_max</t>
+          <t>chart_note_shape</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>bubble</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>commentary_style</t>
+          <t>chart_note_head</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>compose</t>
+          <t>N</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>commentary_disclaimer</t>
+          <t>chart_note_auto_max</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>The Commentary has been generated from the figures in the file and the written commentary carried with it. It may be inaccurate and/or incomplete. It is important to independently review and edit the content before further use or distribution.</t>
+          <t>3</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>commentary_clause_max</t>
+          <t>commentary_style</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>compose</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>ratio_patterns</t>
+          <t>commentary_disclaimer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>%|\bbps\b|\brote\b|\bcer\b|\bratio\b|headcount|\bfte\b|\bcount\b</t>
+          <t>The Commentary has been generated from the figures in the file and the written commentary carried with it. It may be inaccurate and/or incomplete. It is important to independently review and edit the content before further use or distribution.</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>commentary_driver_floor</t>
+          <t>commentary_clause_max</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>150</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>commentary_driver_cover</t>
+          <t>ratio_patterns</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>%|\bbps\b|\brote\b|\bcer\b|\bratio\b|headcount|\bfte\b|\bcount\b</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>commentary_max_notes</t>
+          <t>commentary_driver_floor</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>fsum_notes</t>
+          <t>commentary_driver_cover</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>auto</t>
+          <t>80</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
+        <is>
+          <t>commentary_max_notes</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>fsum_notes</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
         <is>
           <t>fsum_note_lines</t>
         </is>

--- a/iwpb-sg-dashboard/IWPB_dashboard_config_pack.xlsx
+++ b/iwpb-sg-dashboard/IWPB_dashboard_config_pack.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G86"/>
+  <dimension ref="A1:G87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -560,657 +560,657 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>landing_title</t>
+          <t>global_business_prefix</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Financial Performance</t>
+          <t>Global</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>total_label</t>
+          <t>landing_title</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Total P&amp;L</t>
+          <t>Financial Performance</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>total_all_label</t>
+          <t>total_label</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Total (all lines)</t>
+          <t>Total P&amp;L</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>total_tile</t>
+          <t>total_all_label</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>auto</t>
+          <t>Total (all lines)</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>tile_lines</t>
+          <t>total_tile</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>auto</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>tile_metrics</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>auto</t>
+          <t>tile_lines</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>tile_dims</t>
+          <t>tile_metrics</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>auto</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>tile_line_levels</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>micaL1,micaL2</t>
+          <t>tile_dims</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>tile_expand_result</t>
+          <t>tile_line_levels</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>micaL1,micaL2</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>tile_level</t>
+          <t>tile_expand_result</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>auto</t>
+          <t>Y</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>collapse_rest</t>
+          <t>tile_level</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>auto</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>fc_label_pattern</t>
+          <t>collapse_rest</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>forecast|fcst|\bfc\b</t>
+          <t>Y</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>target_label_pattern</t>
+          <t>fc_label_pattern</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>\btarget\b|\btgt\b|target|tgt</t>
+          <t>forecast|fcst|\bfc\b</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>cost_patterns</t>
+          <t>target_label_pattern</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>cost|\becl\b|expected\s+credit|impair|expense</t>
+          <t>\btarget\b|\btgt\b|target|tgt</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>memo_patterns</t>
+          <t>cost_patterns</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>key metric|premier customer|\bcer\b|cost efficiency|\bfte\b|headcount|\bnnm\b|\bnnd\b|\bnnia\b|net new money|invested asset|wealth balance</t>
+          <t>cost|\becl\b|expected\s+credit|impair|expense</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>fsum_memo_label</t>
+          <t>memo_patterns</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Key Metrics</t>
+          <t>key metric|premier customer|\bcer\b|cost efficiency|\bfte\b|headcount|\bnnm\b|\bnnd\b|\bnnia\b|net new money|invested asset|wealth balance</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>balance_sheet_patterns</t>
+          <t>fsum_memo_label</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>deposit|\bloan|advance|mortgage|\bcasa\b|balance|\basset|liabilit|\brwa\b|\baum\b|\bnnm\b|customer\s*account</t>
+          <t>Key Metrics</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>hidden_cmp_patterns</t>
+          <t>balance_sheet_patterns</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>direct\s*costs?|costs?\s*[-–]?\s*(direct|indirect)|indirect\s*costs?|\becl\b|expected\s+credit</t>
+          <t>deposit|\bloan|advance|mortgage|\bcasa\b|balance|\basset|liabilit|\brwa\b|\baum\b|\bnnm\b|customer\s*account</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>dashboard_page_size</t>
+          <t>hidden_cmp_patterns</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>direct\s*costs?|costs?\s*[-–]?\s*(direct|indirect)|indirect\s*costs?|\becl\b|expected\s+credit</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>font_greeting</t>
+          <t>dashboard_page_size</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>6</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>font_commentary</t>
+          <t>font_greeting</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>font_eyebrow</t>
+          <t>font_commentary</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>sim_value_width</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>50</t>
+          <t>font_eyebrow</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>month_case</t>
+          <t>sim_value_width</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>upper</t>
+          <t>50</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>unit_label</t>
+          <t>month_case</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>US$m</t>
+          <t>upper</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>display_units</t>
+          <t>unit_label</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>as</t>
+          <t>US$m</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>unit_options</t>
+          <t>display_units</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>as,k,mm,bn</t>
+          <t>as</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>unit_decimals</t>
+          <t>unit_options</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>as,k,mm,bn</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>variance_periods</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>auto,ytd_py,mom,mth_tgt,ytd_tgt,ytd_fc,fy_tgt,fy_py</t>
+          <t>unit_decimals</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>commentary_dim</t>
+          <t>variance_periods</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>auto,ytd_py,mom,mth_tgt,ytd_tgt,ytd_fc,fy_tgt,fy_py</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>commentary_levels</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>micaL1,micaL2,micaL3</t>
+          <t>commentary_dim</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>commentary_format</t>
+          <t>commentary_levels</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>slide</t>
+          <t>micaL1,micaL2,micaL3</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>commentary_note</t>
+          <t>commentary_format</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>ex notables</t>
+          <t>slide</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>commentary_headline</t>
+          <t>commentary_note</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>FY Forecast</t>
+          <t>ex notables</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>commentary_fa_colours</t>
+          <t>commentary_headline</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>FY Forecast</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>commentary_drivers</t>
+          <t>commentary_fa_colours</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>Y</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>fsum_title</t>
+          <t>commentary_drivers</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Singapore: Financial Summary</t>
+          <t>5</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>fsum_section_label</t>
+          <t>fsum_title</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>P&amp;L</t>
+          <t>Singapore: Financial Summary</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>fsum_section_dim</t>
+          <t>fsum_section_label</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>P&amp;L</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>fsum_section_order</t>
+          <t>fsum_section_dim</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>fsum_sections</t>
+          <t>fsum_section_order</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>fsum_no_total</t>
+          <t>fsum_sections</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>fsum_other_label</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>Other</t>
+          <t>fsum_no_total</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>fsum_total</t>
+          <t>fsum_other_label</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>auto</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>fsum_line_order</t>
+          <t>fsum_total</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>auto</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>fsum_levels</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>accH1,accH2,accH3,cgL2</t>
+          <t>fsum_line_order</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>fsum_max_levels</t>
+          <t>fsum_levels</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>accH1,accH2,accH3,cgL2</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>account_hierarchy_from</t>
+          <t>fsum_max_levels</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>mica,micaL1,micaL2,micaL3,micaL4,micaL5</t>
+          <t>6</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>product_hierarchy_from</t>
+          <t>account_hierarchy_from</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>prodCode,prodL1,prodL2,prodL3</t>
+          <t>mica,micaL1,micaL2,micaL3,micaL4,micaL5</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>hierarchy_unmapped_label</t>
+          <t>product_hierarchy_from</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Unmapped</t>
+          <t>prodCode,prodL1,prodL2,prodL3</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>fsum_ow</t>
+          <t>hierarchy_unmapped_label</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>Unmapped</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>fsum_total_label</t>
+          <t>fsum_ow</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>fsum_residual_label</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>Other</t>
+          <t>fsum_total_label</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>fsum_parent_row</t>
+          <t>fsum_residual_label</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>top</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>fsum_default_levels</t>
+          <t>fsum_parent_row</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>accH1,accH2,accH3</t>
+          <t>top</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>decisions_max</t>
+          <t>fsum_default_levels</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>accH1,accH2,accH3</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>fsum_detail</t>
+          <t>decisions_max</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>3</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>bs_unit</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>bn</t>
+          <t>fsum_detail</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>fsum_bs_label</t>
+          <t>bs_unit</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Balance Sheet</t>
+          <t>bn</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>show_greeting</t>
+          <t>fsum_bs_label</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Balance Sheet</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>commentary_collapsed</t>
+          <t>show_greeting</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -1222,151 +1222,163 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>tile_hidden</t>
+          <t>commentary_collapsed</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>N</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>scorecard_hidden</t>
+          <t>tile_hidden</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>chart_note_shape</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>bubble</t>
+          <t>scorecard_hidden</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>chart_note_head</t>
+          <t>chart_note_shape</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>bubble</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>chart_note_auto_max</t>
+          <t>chart_note_head</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>N</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>commentary_style</t>
+          <t>chart_note_auto_max</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>compose</t>
+          <t>3</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>commentary_disclaimer</t>
+          <t>commentary_style</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>The Commentary has been generated from the figures in the file and the written commentary carried with it. It may be inaccurate and/or incomplete. It is important to independently review and edit the content before further use or distribution.</t>
+          <t>compose</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>commentary_clause_max</t>
+          <t>commentary_disclaimer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>The Commentary has been generated from the figures in the file and the written commentary carried with it. It may be inaccurate and/or incomplete. It is important to independently review and edit the content before further use or distribution.</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>ratio_patterns</t>
+          <t>commentary_clause_max</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>%|\bbps\b|\brote\b|\bcer\b|\bratio\b|headcount|\bfte\b|\bcount\b</t>
+          <t>150</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>commentary_driver_floor</t>
+          <t>ratio_patterns</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>%|\bbps\b|\brote\b|\bcer\b|\bratio\b|headcount|\bfte\b|\bcount\b</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>commentary_driver_cover</t>
+          <t>commentary_driver_floor</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>3</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>commentary_max_notes</t>
+          <t>commentary_driver_cover</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>80</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>fsum_notes</t>
+          <t>commentary_max_notes</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>auto</t>
+          <t>2</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
+        <is>
+          <t>fsum_notes</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
         <is>
           <t>fsum_note_lines</t>
         </is>

--- a/iwpb-sg-dashboard/IWPB_dashboard_config_pack.xlsx
+++ b/iwpb-sg-dashboard/IWPB_dashboard_config_pack.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G87"/>
+  <dimension ref="A1:B87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -883,7 +883,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>auto,ytd_py,mom,mth_tgt,ytd_tgt,ytd_fc,fy_tgt,fy_py</t>
+          <t>qtr_py,ytd_tgt,mth_fc,fy_pfc,fy_py,fy_tgt</t>
         </is>
       </c>
     </row>
@@ -4641,7 +4641,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:B9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -4762,7 +4762,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D8"/>
+  <dimension ref="A1:B8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -5452,7 +5452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:B9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -5578,7 +5578,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D28"/>
+  <dimension ref="A1:B28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>

--- a/iwpb-sg-dashboard/IWPB_dashboard_config_pack.xlsx
+++ b/iwpb-sg-dashboard/IWPB_dashboard_config_pack.xlsx
@@ -19,6 +19,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ProductHierarchy" sheetId="10" state="visible" r:id="rId10"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AccountHierarchy" sheetId="11" state="visible" r:id="rId11"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CountryHierarchy" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CommentaryTemplates" sheetId="13" state="visible" r:id="rId13"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -28,7 +29,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -39,13 +40,22 @@
     <font>
       <b val="1"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00DB0011"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -60,9 +70,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -4635,6 +4646,77 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="110" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>Style</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>Pattern</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Exec brief</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>{line} {var} {vs}, led by {drivers}.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>FP&amp;A detail</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>{line}: {main} against {base} — {varamt} ({varpct}) {vs}. Key movers: {drivers}.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>&lt;i&gt;Tokens: {line} {main} {base} {var} {varamt} {varpct} {vs} {basename} {period} {drivers} {month} {quarter} {fy} {ytd}. View blank = every view. Uploaded rows replace the built-in examples wholesale; the reader picks the style on the Management Commentary panel.</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr"/>
+      <c r="C4" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/iwpb-sg-dashboard/IWPB_dashboard_config_pack.xlsx
+++ b/iwpb-sg-dashboard/IWPB_dashboard_config_pack.xlsx
@@ -925,7 +925,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>slide</t>
+          <t>auto</t>
         </is>
       </c>
     </row>
@@ -4652,12 +4652,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="110" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="100" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4668,7 +4668,7 @@
       </c>
       <c r="B1" s="2" t="inlineStr">
         <is>
-          <t>View</t>
+          <t>Scope</t>
         </is>
       </c>
       <c r="C1" s="2" t="inlineStr">
@@ -4680,37 +4680,105 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Exec brief</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr"/>
+          <t>Group narrative</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Group</t>
+        </is>
+      </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{line} {var} {vs}, led by {drivers}.</t>
+          <t>{line} {var} {vs} across the Group, led by {drivers}.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>FP&amp;A detail</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr"/>
+          <t>IWPB Global</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>IWPB Global</t>
+        </is>
+      </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{line}: {main} against {base} — {varamt} ({varpct}) {vs}. Key movers: {drivers}.</t>
+          <t>{scope}: {line} {var} {vs}, led by {drivers}.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>&lt;i&gt;Tokens: {line} {main} {base} {var} {varamt} {varpct} {vs} {basename} {period} {drivers} {month} {quarter} {fy} {ytd}. View blank = every view. Uploaded rows replace the built-in examples wholesale; the reader picks the style on the Management Commentary panel.</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr"/>
-      <c r="C4" t="inlineStr"/>
+          <t>IWPB Regional</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>IWPB Regional</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>{scope}: {line} {var} {vs} across the region, driven by {drivers}.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>IWPB Country</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>IWPB Country</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>In {scope}, {line} came in at {main}, {var} {vs} on {drivers}.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Exec brief</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>{line} {var} {vs}, led by {drivers}.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>FP&amp;A detail</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>{line}: {main} against {base} — {varamt} ({varpct}) {vs}. Key movers: {drivers}.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>&lt;i&gt;Scope words: Group · Global · Regional · Country, optionally led by a business (IWPB Global) or a place (Singapore). With the style set to Auto — match the scope, the page adopts the best-fitting template as the scope moves; no scoped template defined for a scope means the pack narrative speaks there. A blank scope makes a named style picked by hand.</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/iwpb-sg-dashboard/IWPB_dashboard_config_pack.xlsx
+++ b/iwpb-sg-dashboard/IWPB_dashboard_config_pack.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B87"/>
+  <dimension ref="A1:B88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -1394,6 +1394,14 @@
           <t>fsum_note_lines</t>
         </is>
       </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>tile_visible</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4751,7 +4759,6 @@
           <t>Exec brief</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
           <t>{line} {var} {vs}, led by {drivers}.</t>
@@ -4764,7 +4771,6 @@
           <t>FP&amp;A detail</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr">
         <is>
           <t>{line}: {main} against {base} — {varamt} ({varpct}) {vs}. Key movers: {drivers}.</t>
@@ -4777,8 +4783,6 @@
           <t>&lt;i&gt;Scope words: Group · Global · Regional · Country, optionally led by a business (IWPB Global) or a place (Singapore). With the style set to Auto — match the scope, the page adopts the best-fitting template as the scope moves; no scoped template defined for a scope means the pack narrative speaks there. A blank scope makes a named style picked by hand.</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr"/>
-      <c r="C8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/iwpb-sg-dashboard/IWPB_dashboard_config_pack.xlsx
+++ b/iwpb-sg-dashboard/IWPB_dashboard_config_pack.xlsx
@@ -643,7 +643,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>auto</t>
+          <t>Y</t>
         </is>
       </c>
     </row>
@@ -1401,7 +1401,6 @@
           <t>tile_visible</t>
         </is>
       </c>
-      <c r="B88" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/iwpb-sg-dashboard/IWPB_dashboard_config_pack.xlsx
+++ b/iwpb-sg-dashboard/IWPB_dashboard_config_pack.xlsx
@@ -5890,7 +5890,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Period &amp; RAG</t>
+          <t>Period</t>
         </is>
       </c>
     </row>

--- a/iwpb-sg-dashboard/IWPB_dashboard_config_pack.xlsx
+++ b/iwpb-sg-dashboard/IWPB_dashboard_config_pack.xlsx
@@ -5731,7 +5731,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B28"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -5926,7 +5926,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Load new Driller</t>
+          <t>Ingest TM1 Extract</t>
         </is>
       </c>
     </row>
@@ -6071,6 +6071,30 @@
       <c r="B28" t="inlineStr">
         <is>
           <t>Executive decisions</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>ingest_title</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Ingest TM1 Extract</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>ingest_drop</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Drop the TM1 extract here</t>
         </is>
       </c>
     </row>

--- a/iwpb-sg-dashboard/IWPB_dashboard_config_pack.xlsx
+++ b/iwpb-sg-dashboard/IWPB_dashboard_config_pack.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B88"/>
+  <dimension ref="A1:B90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -1400,6 +1400,26 @@
         <is>
           <t>tile_visible</t>
         </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>tile_height</t>
+        </is>
+      </c>
+      <c r="B89" t="n">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>tile_min_width</t>
+        </is>
+      </c>
+      <c r="B90" t="n">
+        <v>236</v>
       </c>
     </row>
   </sheetData>

--- a/iwpb-sg-dashboard/IWPB_dashboard_config_pack.xlsx
+++ b/iwpb-sg-dashboard/IWPB_dashboard_config_pack.xlsx
@@ -1409,7 +1409,7 @@
         </is>
       </c>
       <c r="B89" t="n">
-        <v>124</v>
+        <v>150</v>
       </c>
     </row>
     <row r="90">
@@ -1419,7 +1419,7 @@
         </is>
       </c>
       <c r="B90" t="n">
-        <v>236</v>
+        <v>252</v>
       </c>
     </row>
   </sheetData>

--- a/iwpb-sg-dashboard/IWPB_dashboard_config_pack.xlsx
+++ b/iwpb-sg-dashboard/IWPB_dashboard_config_pack.xlsx
@@ -5751,7 +5751,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -6115,6 +6115,30 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>Drop the TM1 extract here</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>nav_bizperf</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Business performance</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>nav_comall</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>All commentaries</t>
         </is>
       </c>
     </row>

--- a/iwpb-sg-dashboard/IWPB_dashboard_config_pack.xlsx
+++ b/iwpb-sg-dashboard/IWPB_dashboard_config_pack.xlsx
@@ -5946,7 +5946,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Ingest TM1 Extract</t>
+          <t>Ingest TM1 Data Extract</t>
         </is>
       </c>
     </row>
@@ -6102,7 +6102,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Ingest TM1 Extract</t>
+          <t>Ingest TM1 Data Extract</t>
         </is>
       </c>
     </row>
@@ -6114,7 +6114,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Drop the TM1 extract here</t>
+          <t>Drop the TM1 data extract here</t>
         </is>
       </c>
     </row>

--- a/iwpb-sg-dashboard/IWPB_dashboard_config_pack.xlsx
+++ b/iwpb-sg-dashboard/IWPB_dashboard_config_pack.xlsx
@@ -45,7 +45,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -55,6 +55,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00DB0011"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="009E1B32"/>
       </patternFill>
     </fill>
   </fills>
@@ -70,10 +75,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -5751,20 +5757,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B32"/>
+  <dimension ref="A1:B27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="52" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="46" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="3" t="inlineStr">
         <is>
           <t>Key</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="3" t="inlineStr">
         <is>
           <t>Text</t>
         </is>
@@ -5821,72 +5827,72 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>nav_table</t>
+          <t>nav_assist</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Data drill down</t>
+          <t>MI Assistant</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>nav_assist</t>
+          <t>nav_sim</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>MI Assistant</t>
+          <t>Simulation Assistant</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>nav_sim</t>
+          <t>nav_fsum</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Simulation Assistant</t>
+          <t>Financial Summary</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>nav_fsum</t>
+          <t>nav_comall</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Financial Summary</t>
+          <t>All commentaries</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>sect_dashboards</t>
+          <t>nav_bizperf</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>KPI Dashboards</t>
+          <t>Business performance</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>sect_kpis</t>
+          <t>sect_dashboards</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>KPIs · MICA Level 2</t>
+          <t>KPI Dashboards</t>
         </is>
       </c>
     </row>
@@ -5917,31 +5923,31 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>sect_filters</t>
+          <t>sect_comtpl</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Filters — all columns</t>
+          <t>Commentary templates</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>sect_output</t>
+          <t>btn_newfile</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Output fields</t>
+          <t>Ingest TM1 Data Extract</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>btn_newfile</t>
+          <t>ingest_title</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -5953,12 +5959,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>sect_drivers</t>
+          <t>ingest_drop</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Drivers · AI commentary</t>
+          <t>Drop the TM1 data extract here</t>
         </is>
       </c>
     </row>
@@ -5989,12 +5995,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>drv_hint</t>
+          <t>lbl_year</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Known business drivers — the AI weaves them into chart commentary wherever the line appears as a mover.</t>
+          <t>Year</t>
         </is>
       </c>
     </row>
@@ -6013,132 +6019,72 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>lbl_fc</t>
+          <t>lbl_varper</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Include forecast month</t>
+          <t>Variance period</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>lbl_tol</t>
+          <t>lbl_units</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>RAG tolerance</t>
+          <t>Units</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>lbl_varper</t>
+          <t>lbl_scope</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Variance period</t>
+          <t>Scope</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>lbl_units</t>
+          <t>lbl_tplpick</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Units</t>
+          <t>Active style</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>kpi_hint</t>
+          <t>dec_eyebrow</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Click a KPI to see its trajectory and commentary · drag one onto My dashboard to add a card</t>
+          <t>Decisions required</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>dec_eyebrow</t>
+          <t>dec_title</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Decisions required</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>dec_title</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
           <t>Executive decisions</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>ingest_title</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Ingest TM1 Data Extract</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>ingest_drop</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>Drop the TM1 data extract here</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>nav_bizperf</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>Business performance</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>nav_comall</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>All commentaries</t>
         </is>
       </c>
     </row>
